--- a/GHG_Calculation/output/country_reduction_and_sludge.xlsx
+++ b/GHG_Calculation/output/country_reduction_and_sludge.xlsx
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8708973006839812</v>
+        <v>0.8698590817042412</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5671784054716414</v>
+        <v>0.5588726536336511</v>
       </c>
       <c r="D2" t="n">
-        <v>0.497642799810937</v>
+        <v>0.4892880196279627</v>
       </c>
       <c r="E2" t="n">
         <v>32.66086706493564</v>
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8647067696523459</v>
+        <v>0.8647898296282166</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5176541572182632</v>
+        <v>0.518318637025221</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5370435735385881</v>
+        <v>0.5405878785472339</v>
       </c>
       <c r="E4" t="n">
         <v>11.540024195441</v>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8711235301672789</v>
+        <v>0.8705121602938396</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5689882413380623</v>
+        <v>0.5640972823505257</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5318917050578538</v>
+        <v>0.5348421186563453</v>
       </c>
       <c r="E5" t="n">
         <v>467.9482161463221</v>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8573500000001099</v>
+        <v>0.8574750000001117</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4588000000000304</v>
+        <v>0.4598000000000279</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3226849779751461</v>
+        <v>0.3228131895877066</v>
       </c>
       <c r="E6" t="n">
         <v>0.7749488912686271</v>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8680229158379514</v>
+        <v>0.8675955721962465</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5441833267036338</v>
+        <v>0.5407645775699843</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5418919455351442</v>
+        <v>0.5423302326736528</v>
       </c>
       <c r="E8" t="n">
         <v>113.3609473704607</v>
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8669700000000501</v>
+        <v>0.866735000000051</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5357600000000088</v>
+        <v>0.5338800000000097</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4454885015184734</v>
+        <v>0.445194515010633</v>
       </c>
       <c r="E10" t="n">
         <v>0.2345335899922497</v>
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7234889088622772</v>
+        <v>0.723193167170446</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3926708962802393</v>
+        <v>0.3903049627455805</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4855339249465725</v>
+        <v>0.4865037318057885</v>
       </c>
       <c r="E11" t="n">
         <v>204.2965708905447</v>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8714812763702696</v>
+        <v>0.8713291076358526</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5718502109619119</v>
+        <v>0.570632861086557</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5395621679212647</v>
+        <v>0.5398692009996047</v>
       </c>
       <c r="E12" t="n">
         <v>0.08487414272203886</v>
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8598684047944277</v>
+        <v>0.8594077743130371</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4789472383550847</v>
+        <v>0.4752621945039819</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5540430804661055</v>
+        <v>0.5544766764413601</v>
       </c>
       <c r="E13" t="n">
         <v>0.305437759099393</v>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8642333278092109</v>
+        <v>0.8644258748313394</v>
       </c>
       <c r="C14" t="n">
-        <v>0.513960209078009</v>
+        <v>0.5155005852550394</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4955629633960575</v>
+        <v>0.4977601493942377</v>
       </c>
       <c r="E14" t="n">
         <v>545.0186758348129</v>
@@ -759,7 +759,7 @@
         <v>0.8000000000001272</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5659324049136224</v>
+        <v>0.5620557855311379</v>
       </c>
       <c r="E15" t="n">
         <v>190.451771946259</v>
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4325645069411059</v>
+        <v>0.4322423894577781</v>
       </c>
       <c r="C16" t="n">
-        <v>0.336389225876384</v>
+        <v>0.3338122860097529</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2931030937598743</v>
+        <v>0.2938232945494927</v>
       </c>
       <c r="E16" t="n">
         <v>61.12084472967302</v>
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8592555057596166</v>
+        <v>0.8588220257515063</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4740440460762002</v>
+        <v>0.4705762060112749</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5748771148110753</v>
+        <v>0.5783743668928958</v>
       </c>
       <c r="E17" t="n">
         <v>1.361251531529879</v>
@@ -825,7 +825,7 @@
         <v>0.7986480407653177</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6144889566731931</v>
+        <v>0.6138339473626084</v>
       </c>
       <c r="E18" t="n">
         <v>19.58896282613744</v>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1371408445268089</v>
+        <v>0.137163289735381</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08325873090423519</v>
+        <v>0.08343829257281365</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08053886071426646</v>
+        <v>0.07945146055999806</v>
       </c>
       <c r="E19" t="n">
         <v>262.6245105542387</v>
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8598450000000943</v>
+        <v>0.8604250000000949</v>
       </c>
       <c r="C20" t="n">
-        <v>0.47876000000002</v>
+        <v>0.4834000000000168</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5862470414582517</v>
+        <v>0.5853469538171298</v>
       </c>
       <c r="E20" t="n">
         <v>0.08903963616257703</v>
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8638667523639119</v>
+        <v>0.8632512963444195</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5109340189110392</v>
+        <v>0.5060103707550838</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4749418278143651</v>
+        <v>0.4758941981572348</v>
       </c>
       <c r="E21" t="n">
         <v>160.2541287757626</v>
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8991815510527763</v>
+        <v>0.899181181947116</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7934524084233209</v>
+        <v>0.7934494555780405</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5138158802990834</v>
+        <v>0.5126427389695974</v>
       </c>
       <c r="E22" t="n">
         <v>211.5044411601622</v>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8629754175537137</v>
+        <v>0.8623938009723946</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5038033404290899</v>
+        <v>0.4991504077784928</v>
       </c>
       <c r="D23" t="n">
-        <v>0.467617620699962</v>
+        <v>0.4701731191615655</v>
       </c>
       <c r="E23" t="n">
         <v>0.5247485309307651</v>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.850652305101277</v>
+        <v>0.8506532524032193</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4052184408111509</v>
+        <v>0.4052260192267007</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4049983052738257</v>
+        <v>0.4050140986573901</v>
       </c>
       <c r="E26" t="n">
         <v>2.627378451347528</v>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8505055904999738</v>
+        <v>0.8504903317893318</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4040447239986258</v>
+        <v>0.4039226543134884</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2006088978375995</v>
+        <v>0.2010389158179655</v>
       </c>
       <c r="E27" t="n">
         <v>21.85194997189336</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8891011805998731</v>
+        <v>0.8889916687938754</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7128094447989791</v>
+        <v>0.7119333503509895</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6032332277810685</v>
+        <v>0.6048384384641349</v>
       </c>
       <c r="E29" t="n">
         <v>32.02259778570582</v>
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8500215561702634</v>
+        <v>0.8500192391062086</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4001724493609954</v>
+        <v>0.4001539128485512</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3948224118542146</v>
+        <v>0.3948377822366183</v>
       </c>
       <c r="E30" t="n">
         <v>0.8599390944454363</v>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8605530831769991</v>
+        <v>0.859885587703256</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4844246654156821</v>
+        <v>0.4790847016257207</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5332779638145739</v>
+        <v>0.5367324205720707</v>
       </c>
       <c r="E31" t="n">
         <v>1596.255156591014</v>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8580550000001083</v>
+        <v>0.8579200000001078</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4644400000000258</v>
+        <v>0.4633600000000248</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5863583334981703</v>
+        <v>0.5872592835848074</v>
       </c>
       <c r="E32" t="n">
         <v>0.08320769692841738</v>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8592781092654083</v>
+        <v>0.8585469515988826</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4742248741224987</v>
+        <v>0.4683756127902381</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5849732020400287</v>
+        <v>0.5878655067525999</v>
       </c>
       <c r="E33" t="n">
         <v>1.231816808860491</v>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8911527457983281</v>
+        <v>0.8910540396723693</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7292219663873708</v>
+        <v>0.7284323173796975</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5923463618997519</v>
+        <v>0.5944603646615189</v>
       </c>
       <c r="E34" t="n">
         <v>104.7077617073601</v>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1210192925034337</v>
+        <v>0.1208680967726885</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07630855498287488</v>
+        <v>0.07509898913690854</v>
       </c>
       <c r="D35" t="n">
-        <v>0.07561864577434257</v>
+        <v>0.07447335425781272</v>
       </c>
       <c r="E35" t="n">
         <v>4.154500571207591</v>
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8564457428532803</v>
+        <v>0.8562803814100847</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4515659428253334</v>
+        <v>0.450243051279767</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5319065384956499</v>
+        <v>0.5251241182540973</v>
       </c>
       <c r="E37" t="n">
         <v>65.083016592487</v>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2074078103099967</v>
+        <v>0.2072236127677737</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1265099306032444</v>
+        <v>0.1250363502654501</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1181974091966324</v>
+        <v>0.1183368383060149</v>
       </c>
       <c r="E38" t="n">
         <v>33.77721231859899</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8622524658043993</v>
+        <v>0.8621827632413415</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4980197264347911</v>
+        <v>0.4974621059303297</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4295838329984449</v>
+        <v>0.4299432180872564</v>
       </c>
       <c r="E39" t="n">
         <v>533.2690040895898</v>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8559665885368151</v>
+        <v>0.8563189308489989</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4477327082937216</v>
+        <v>0.450551446791228</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3344386353644433</v>
+        <v>0.3365751960215659</v>
       </c>
       <c r="E40" t="n">
         <v>0.8095931277627545</v>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.859629942273803</v>
+        <v>0.8581933981501814</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4770395381896244</v>
+        <v>0.4655471852006038</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2909114694809318</v>
+        <v>0.2764677943012861</v>
       </c>
       <c r="E43" t="n">
         <v>3.954078536032042</v>
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8597148619603</v>
+        <v>0.8589269191965628</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4777188956817819</v>
+        <v>0.4714153535718289</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5576275970793625</v>
+        <v>0.5554711625697947</v>
       </c>
       <c r="E44" t="n">
         <v>247.7306291343294</v>
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.895790453616002</v>
+        <v>0.8957661479594214</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7663236289286376</v>
+        <v>0.7661291836759925</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6208169673550962</v>
+        <v>0.62085767845142</v>
       </c>
       <c r="E45" t="n">
         <v>12360.81837952406</v>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8606323657904924</v>
+        <v>0.8601969635628466</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4850589263233976</v>
+        <v>0.4815757085022019</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5593437179500661</v>
+        <v>0.5612128215981107</v>
       </c>
       <c r="E48" t="n">
         <v>120.2131616196006</v>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8580106172840786</v>
+        <v>0.8570022183643232</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4640849382716131</v>
+        <v>0.4560177469135957</v>
       </c>
       <c r="D50" t="n">
-        <v>0.545374613235298</v>
+        <v>0.5508708124707495</v>
       </c>
       <c r="E50" t="n">
         <v>0.1857289562236455</v>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8574855980954116</v>
+        <v>0.8572486078059717</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4598847847626655</v>
+        <v>0.457988862447149</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5834798766709357</v>
+        <v>0.5835322291270718</v>
       </c>
       <c r="E51" t="n">
         <v>8.824061756260082</v>
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8376268598031564</v>
+        <v>0.8371523783260122</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5324759576848709</v>
+        <v>0.528680105867692</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5565855429175379</v>
+        <v>0.5583167323104797</v>
       </c>
       <c r="E52" t="n">
         <v>22.97953749729641</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8733791484968877</v>
+        <v>0.8730962687736326</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5870331879750291</v>
+        <v>0.5847701501889866</v>
       </c>
       <c r="D53" t="n">
-        <v>0.5848945498823456</v>
+        <v>0.5883503666899612</v>
       </c>
       <c r="E53" t="n">
         <v>48.28534716383739</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8615850000000864</v>
+        <v>0.8615800000000832</v>
       </c>
       <c r="C54" t="n">
-        <v>0.492680000000015</v>
+        <v>0.4926400000000159</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5798887480021058</v>
+        <v>0.5832975882956244</v>
       </c>
       <c r="E54" t="n">
         <v>0.6148971656318029</v>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8974685413840581</v>
+        <v>0.897457920946645</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7797483310726327</v>
+        <v>0.7796633675733164</v>
       </c>
       <c r="D55" t="n">
-        <v>0.590055973390714</v>
+        <v>0.5922279015811596</v>
       </c>
       <c r="E55" t="n">
         <v>11.7756668627214</v>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8937079801809087</v>
+        <v>0.8936042559045478</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7496638414477543</v>
+        <v>0.7488340472368619</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5775730788730166</v>
+        <v>0.5803652380493958</v>
       </c>
       <c r="E56" t="n">
         <v>204.8855153266217</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8684114752429428</v>
+        <v>0.8696419281216632</v>
       </c>
       <c r="C57" t="n">
-        <v>0.5472918019435697</v>
+        <v>0.5571354249733187</v>
       </c>
       <c r="D57" t="n">
-        <v>0.5494266047704969</v>
+        <v>0.5476350610761602</v>
       </c>
       <c r="E57" t="n">
         <v>36.76463424912802</v>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.862629274488918</v>
+        <v>0.8624884761713668</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5010341959107084</v>
+        <v>0.4999078093702924</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5138778076429364</v>
+        <v>0.4999760769157736</v>
       </c>
       <c r="E58" t="n">
         <v>83.82501542906645</v>
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.898301602995831</v>
+        <v>0.8982966955299335</v>
       </c>
       <c r="C59" t="n">
-        <v>0.786412823966998</v>
+        <v>0.7863735642398175</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5401981189107177</v>
+        <v>0.5369986977784416</v>
       </c>
       <c r="E59" t="n">
         <v>127.7962919778168</v>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8582868839727184</v>
+        <v>0.8576534859312971</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4662950717809214</v>
+        <v>0.4612278874495205</v>
       </c>
       <c r="D63" t="n">
-        <v>0.5478764315206965</v>
+        <v>0.5497605466071322</v>
       </c>
       <c r="E63" t="n">
         <v>41.03113763953981</v>
@@ -1831,13 +1831,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8684944382598572</v>
+        <v>0.868008197101624</v>
       </c>
       <c r="C64" t="n">
-        <v>0.54795550607863</v>
+        <v>0.544065576812748</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5047931363782301</v>
+        <v>0.5100717277937765</v>
       </c>
       <c r="E64" t="n">
         <v>941.9812614618061</v>
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8588995959522705</v>
+        <v>0.8585116761416979</v>
       </c>
       <c r="C65" t="n">
-        <v>0.471196767617363</v>
+        <v>0.468093409132776</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3844345616909098</v>
+        <v>0.3896303623963252</v>
       </c>
       <c r="E65" t="n">
         <v>10.116556045104</v>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.2166099549266779</v>
+        <v>0.2162130128216009</v>
       </c>
       <c r="C66" t="n">
-        <v>0.159858294206655</v>
+        <v>0.1566827573660176</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1454553064283953</v>
+        <v>0.1466802718635917</v>
       </c>
       <c r="E66" t="n">
         <v>5.372153676323486</v>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8996567600467464</v>
+        <v>0.8996560315910362</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7972540803753968</v>
+        <v>0.7972482527297152</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5979674058128455</v>
+        <v>0.6000326587602678</v>
       </c>
       <c r="E68" t="n">
         <v>25.87459710857619</v>
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8618139415903624</v>
+        <v>0.8617614002349985</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4945115327229312</v>
+        <v>0.4940912018799922</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5732597559196956</v>
+        <v>0.5738756850667339</v>
       </c>
       <c r="E69" t="n">
         <v>30.87690695241073</v>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6957149336886466</v>
+        <v>0.6952473402601529</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3980904046089807</v>
+        <v>0.3943496571810362</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3221440258567683</v>
+        <v>0.3232544957177692</v>
       </c>
       <c r="E72" t="n">
         <v>4.438690535032757</v>
@@ -2035,7 +2035,7 @@
         <v>0.8000000000001271</v>
       </c>
       <c r="D73" t="n">
-        <v>0.5397519577427916</v>
+        <v>0.5369747676258191</v>
       </c>
       <c r="E73" t="n">
         <v>105.3132747551247</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8771629701258448</v>
+        <v>0.8771693809892535</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6173037610068774</v>
+        <v>0.6173550479141476</v>
       </c>
       <c r="D74" t="n">
-        <v>0.53330973760456</v>
+        <v>0.5333044450186478</v>
       </c>
       <c r="E74" t="n">
         <v>1171.41911275185</v>
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8530149074737192</v>
+        <v>0.8528463322516434</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4241192597888728</v>
+        <v>0.4227706580122663</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4649877314915037</v>
+        <v>0.4652991551147995</v>
       </c>
       <c r="E75" t="n">
         <v>2.524901650128266</v>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8546100000001261</v>
+        <v>0.8545800000001307</v>
       </c>
       <c r="C76" t="n">
-        <v>0.436880000000042</v>
+        <v>0.4366400000000414</v>
       </c>
       <c r="D76" t="n">
-        <v>0.5989847299056837</v>
+        <v>0.6007740594267224</v>
       </c>
       <c r="E76" t="n">
         <v>2.011739568917036</v>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.03257434697286951</v>
+        <v>0.03251985747964958</v>
       </c>
       <c r="C77" t="n">
-        <v>0.01925722795684805</v>
+        <v>0.01882131201108735</v>
       </c>
       <c r="D77" t="n">
-        <v>0.01642315636303339</v>
+        <v>0.0162007706720859</v>
       </c>
       <c r="E77" t="n">
         <v>7.663367558884807</v>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.153736174445171</v>
+        <v>0.1535644523641478</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1026880432001114</v>
+        <v>0.1013142665519211</v>
       </c>
       <c r="D78" t="n">
-        <v>0.08516256224015303</v>
+        <v>0.08377167794568488</v>
       </c>
       <c r="E78" t="n">
         <v>1.643587266815097</v>
@@ -2161,13 +2161,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.1913145968951804</v>
+        <v>0.1912386142950717</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1212336821272328</v>
+        <v>0.1206258213263614</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1162656103631069</v>
+        <v>0.1166616757806136</v>
       </c>
       <c r="E79" t="n">
         <v>26.54078036938848</v>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8998799098973929</v>
+        <v>0.8998817644734719</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7990392791804274</v>
+        <v>0.7990541157890616</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5187283695866415</v>
+        <v>0.5171312997465582</v>
       </c>
       <c r="E80" t="n">
         <v>1877.814417424976</v>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4048582322212163</v>
+        <v>0.4051881072120837</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2576589749511423</v>
+        <v>0.2602979748780882</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2372837176812136</v>
+        <v>0.2417440155962868</v>
       </c>
       <c r="E81" t="n">
         <v>26.45235485744499</v>
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.85784000000011</v>
+        <v>0.8579700000001101</v>
       </c>
       <c r="C82" t="n">
-        <v>0.4627200000000256</v>
+        <v>0.4637600000000272</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6059540958980809</v>
+        <v>0.6074921380499996</v>
       </c>
       <c r="E82" t="n">
         <v>0.6013128743064914</v>
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8970561980197763</v>
+        <v>0.8970104608802817</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7764495841589949</v>
+        <v>0.776083687043032</v>
       </c>
       <c r="D83" t="n">
-        <v>0.5974044706164023</v>
+        <v>0.5992387944828578</v>
       </c>
       <c r="E83" t="n">
         <v>187.6609093424933</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8694845280362957</v>
+        <v>0.8696232522803683</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5558762242903612</v>
+        <v>0.5569860182429354</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5742096293982667</v>
+        <v>0.5738640629502767</v>
       </c>
       <c r="E86" t="n">
         <v>1.256142605680493</v>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8540027588180538</v>
+        <v>0.8538678142493132</v>
       </c>
       <c r="C87" t="n">
-        <v>0.4320220705439795</v>
+        <v>0.4309425139940394</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5917367559567609</v>
+        <v>0.5923851771126494</v>
       </c>
       <c r="E87" t="n">
         <v>1.591780757728001</v>
@@ -2359,13 +2359,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8749569421568434</v>
+        <v>0.8753617381679384</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5996555372547521</v>
+        <v>0.602893905343483</v>
       </c>
       <c r="D88" t="n">
-        <v>0.5937670684134444</v>
+        <v>0.5975599397293836</v>
       </c>
       <c r="E88" t="n">
         <v>27.34173940478406</v>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.869806471664004</v>
+        <v>0.8702272638027738</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5584517733117794</v>
+        <v>0.5618181104219702</v>
       </c>
       <c r="D90" t="n">
-        <v>0.5354283932228414</v>
+        <v>0.5214029543414581</v>
       </c>
       <c r="E90" t="n">
         <v>3.246376235315545</v>
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4226047421987345</v>
+        <v>0.4226194258264107</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2718596910571892</v>
+        <v>0.2719771600786026</v>
       </c>
       <c r="D93" t="n">
-        <v>0.241968004542149</v>
+        <v>0.2386160686754033</v>
       </c>
       <c r="E93" t="n">
         <v>13.63328011919963</v>
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8633973172515332</v>
+        <v>0.8653855409357301</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5071785380116942</v>
+        <v>0.5230843274853771</v>
       </c>
       <c r="D94" t="n">
-        <v>0.430187231952338</v>
+        <v>0.4799734743000372</v>
       </c>
       <c r="E94" t="n">
         <v>17.59346558599538</v>
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8948673143989028</v>
+        <v>0.8947870200324574</v>
       </c>
       <c r="C96" t="n">
-        <v>0.7589385151919275</v>
+        <v>0.7582961602603624</v>
       </c>
       <c r="D96" t="n">
-        <v>0.5888228018685622</v>
+        <v>0.5911836416210675</v>
       </c>
       <c r="E96" t="n">
         <v>167.3022352731821</v>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.8341481987235814</v>
+        <v>0.8339332909986225</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5136669418352465</v>
+        <v>0.5119476800355645</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4532123435302184</v>
+        <v>0.4594340382325445</v>
       </c>
       <c r="E97" t="n">
         <v>0.1006104691990836</v>
@@ -2579,13 +2579,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8691672855858368</v>
+        <v>0.8691650398340239</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5533382846869199</v>
+        <v>0.5533203186724154</v>
       </c>
       <c r="D98" t="n">
-        <v>0.516871814911844</v>
+        <v>0.5165729435498346</v>
       </c>
       <c r="E98" t="n">
         <v>1755.97684711638</v>
@@ -2601,13 +2601,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8620733703678307</v>
+        <v>0.8622053312979057</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4965869629421686</v>
+        <v>0.4976426503827778</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4576278631527159</v>
+        <v>0.4656634052784871</v>
       </c>
       <c r="E99" t="n">
         <v>1125.413238594529</v>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8836591121202845</v>
+        <v>0.8834898444715569</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6692728969626488</v>
+        <v>0.6679187557728226</v>
       </c>
       <c r="D100" t="n">
-        <v>0.5903398296786565</v>
+        <v>0.5942476821916668</v>
       </c>
       <c r="E100" t="n">
         <v>325.7134580749318</v>
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8833557157339891</v>
+        <v>0.8826543473287772</v>
       </c>
       <c r="C101" t="n">
-        <v>0.6668457258722847</v>
+        <v>0.6612347786305472</v>
       </c>
       <c r="D101" t="n">
-        <v>0.5744576480689082</v>
+        <v>0.5744703580540025</v>
       </c>
       <c r="E101" t="n">
         <v>197.1139776746488</v>
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8702130043630828</v>
+        <v>0.8698263268840183</v>
       </c>
       <c r="C102" t="n">
-        <v>0.5617040349046577</v>
+        <v>0.558610615072164</v>
       </c>
       <c r="D102" t="n">
-        <v>0.5525934732155655</v>
+        <v>0.5542806832304763</v>
       </c>
       <c r="E102" t="n">
         <v>45.36498913024482</v>
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.8622929385632235</v>
+        <v>0.861373906955983</v>
       </c>
       <c r="C104" t="n">
-        <v>0.4983435085055212</v>
+        <v>0.490991255647577</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5842051897383008</v>
+        <v>0.5869732982602702</v>
       </c>
       <c r="E104" t="n">
         <v>130.2092315822918</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.8874199145742712</v>
+        <v>0.887291670544667</v>
       </c>
       <c r="C105" t="n">
-        <v>0.6993593165943518</v>
+        <v>0.698333364357519</v>
       </c>
       <c r="D105" t="n">
-        <v>0.5900751070546889</v>
+        <v>0.5918218502145077</v>
       </c>
       <c r="E105" t="n">
         <v>918.6978249115692</v>
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8859914696014929</v>
+        <v>0.8863526455468418</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6879317568120974</v>
+        <v>0.690821164374862</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5455460117373863</v>
+        <v>0.5477165335584938</v>
       </c>
       <c r="E106" t="n">
         <v>6.618300317912715</v>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8623187008488649</v>
+        <v>0.8622903981688094</v>
       </c>
       <c r="C107" t="n">
-        <v>0.4985496067908967</v>
+        <v>0.4983231853504524</v>
       </c>
       <c r="D107" t="n">
-        <v>0.6195323323933838</v>
+        <v>0.6195834652310944</v>
       </c>
       <c r="E107" t="n">
         <v>1646.006230776668</v>
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.8645692833988399</v>
+        <v>0.8643815774759205</v>
       </c>
       <c r="C110" t="n">
-        <v>0.5165542671902749</v>
+        <v>0.5150526198069083</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4665082481542653</v>
+        <v>0.4697817080993827</v>
       </c>
       <c r="E110" t="n">
         <v>98.90351876764261</v>
@@ -2865,13 +2865,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.8645579827360702</v>
+        <v>0.8637568181126931</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5164638618883944</v>
+        <v>0.5100545449013544</v>
       </c>
       <c r="D111" t="n">
-        <v>0.5345918978759575</v>
+        <v>0.5302954849159505</v>
       </c>
       <c r="E111" t="n">
         <v>60.72958486528761</v>
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.8677348991311968</v>
+        <v>0.8673245561843181</v>
       </c>
       <c r="C113" t="n">
-        <v>0.5418791930492485</v>
+        <v>0.5385964494742135</v>
       </c>
       <c r="D113" t="n">
-        <v>0.5538813501554484</v>
+        <v>0.5563338103719402</v>
       </c>
       <c r="E113" t="n">
         <v>6.780005281942866</v>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.8681274116873352</v>
+        <v>0.8677586100344468</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5450192934981205</v>
+        <v>0.5420688802749764</v>
       </c>
       <c r="D114" t="n">
-        <v>0.5694485982987664</v>
+        <v>0.5721649765996009</v>
       </c>
       <c r="E114" t="n">
         <v>67.69462285284881</v>
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.8601951998359899</v>
+        <v>0.8595732407958854</v>
       </c>
       <c r="C115" t="n">
-        <v>0.4815615986874085</v>
+        <v>0.4765859263665425</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4761206989164284</v>
+        <v>0.4768304741084787</v>
       </c>
       <c r="E115" t="n">
         <v>18.59173336297502</v>
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.8646646948724581</v>
+        <v>0.8644067777823941</v>
       </c>
       <c r="C116" t="n">
-        <v>0.517317558979253</v>
+        <v>0.515254222258714</v>
       </c>
       <c r="D116" t="n">
-        <v>0.395362643751494</v>
+        <v>0.3887354557901008</v>
       </c>
       <c r="E116" t="n">
         <v>30.61303979225888</v>
@@ -2997,13 +2997,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.8907625505888617</v>
+        <v>0.8906638254985755</v>
       </c>
       <c r="C117" t="n">
-        <v>0.7261004047107903</v>
+        <v>0.7253106039884872</v>
       </c>
       <c r="D117" t="n">
-        <v>0.5562092395106506</v>
+        <v>0.5584388598484328</v>
       </c>
       <c r="E117" t="n">
         <v>34.47233010727909</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.309404989314273</v>
+        <v>0.3091677943448737</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1833170181614835</v>
+        <v>0.1814194584062701</v>
       </c>
       <c r="D118" t="n">
-        <v>0.2102870222654674</v>
+        <v>0.2106139928100088</v>
       </c>
       <c r="E118" t="n">
         <v>72.06803766276001</v>
@@ -3041,13 +3041,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.8689994915561396</v>
+        <v>0.8680058535749161</v>
       </c>
       <c r="C119" t="n">
-        <v>0.5519959324489327</v>
+        <v>0.5440468285991165</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4655812108631293</v>
+        <v>0.4574301469698632</v>
       </c>
       <c r="E119" t="n">
         <v>0.7373481444797095</v>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.05029234663993899</v>
+        <v>0.05023813824399015</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0312866511124794</v>
+        <v>0.03085298394488367</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0278684572433079</v>
+        <v>0.02721153116223637</v>
       </c>
       <c r="E120" t="n">
         <v>9.71087563394569</v>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.8856983650458864</v>
+        <v>0.8855707724203726</v>
       </c>
       <c r="C121" t="n">
-        <v>0.6855869203674443</v>
+        <v>0.6845661793632997</v>
       </c>
       <c r="D121" t="n">
-        <v>0.5949698374079404</v>
+        <v>0.5967427688813607</v>
       </c>
       <c r="E121" t="n">
         <v>11.96089169256979</v>
@@ -3129,13 +3129,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.899444961214197</v>
+        <v>0.8994399169041279</v>
       </c>
       <c r="C123" t="n">
-        <v>0.7955596897147877</v>
+        <v>0.7955193352342368</v>
       </c>
       <c r="D123" t="n">
-        <v>0.5941952321879905</v>
+        <v>0.5982421223813286</v>
       </c>
       <c r="E123" t="n">
         <v>60.8766467888271</v>
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.8972697130667165</v>
+        <v>0.8972668312688663</v>
       </c>
       <c r="C124" t="n">
-        <v>0.7781577045347312</v>
+        <v>0.7781346501519385</v>
       </c>
       <c r="D124" t="n">
-        <v>0.5640040747470199</v>
+        <v>0.56189730233582</v>
       </c>
       <c r="E124" t="n">
         <v>14.22909363780239</v>
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.8679852769178614</v>
+        <v>0.8674705842647702</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5438822153425109</v>
+        <v>0.5397646741177716</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4649468894414375</v>
+        <v>0.4661991513166367</v>
       </c>
       <c r="E126" t="n">
         <v>1.470306596834171</v>
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.06131828114381066</v>
+        <v>0.06126341773011821</v>
       </c>
       <c r="C127" t="n">
-        <v>0.03772487825196177</v>
+        <v>0.0372859709424187</v>
       </c>
       <c r="D127" t="n">
-        <v>0.03019968881188076</v>
+        <v>0.0297502926464623</v>
       </c>
       <c r="E127" t="n">
         <v>20.67057795657171</v>
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.858189266714069</v>
+        <v>0.8575153807745829</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4655141337121895</v>
+        <v>0.4601230461962753</v>
       </c>
       <c r="D129" t="n">
-        <v>0.5733771529387816</v>
+        <v>0.5772556362106565</v>
       </c>
       <c r="E129" t="n">
         <v>435.0801087999362</v>
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.8647478493487046</v>
+        <v>0.8648734482321409</v>
       </c>
       <c r="C130" t="n">
-        <v>0.5179827947893788</v>
+        <v>0.5189875858568844</v>
       </c>
       <c r="D130" t="n">
-        <v>0.5063830529115508</v>
+        <v>0.5010545518165133</v>
       </c>
       <c r="E130" t="n">
         <v>3.268104057078799</v>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.8732229586960425</v>
+        <v>0.8728095650218802</v>
       </c>
       <c r="C131" t="n">
-        <v>0.585783669568271</v>
+        <v>0.582476520174941</v>
       </c>
       <c r="D131" t="n">
-        <v>0.5153247141801558</v>
+        <v>0.512881554019765</v>
       </c>
       <c r="E131" t="n">
         <v>10.25328921009218</v>
@@ -3327,13 +3327,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4768877935128701</v>
+        <v>0.4768404744636348</v>
       </c>
       <c r="C132" t="n">
-        <v>0.4080912278600887</v>
+        <v>0.4077126754661994</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3208696145434382</v>
+        <v>0.322267137480698</v>
       </c>
       <c r="E132" t="n">
         <v>0.1318243638473373</v>
@@ -3349,13 +3349,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.8599400000000962</v>
+        <v>0.8605750000000894</v>
       </c>
       <c r="C133" t="n">
-        <v>0.4795200000000182</v>
+        <v>0.4846000000000196</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3287519592946704</v>
+        <v>0.3409636714890691</v>
       </c>
       <c r="E133" t="n">
         <v>0.3980591203641774</v>
@@ -3371,13 +3371,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.8855394596223075</v>
+        <v>0.8855336276304901</v>
       </c>
       <c r="C134" t="n">
-        <v>0.6843156769782942</v>
+        <v>0.6842690210437458</v>
       </c>
       <c r="D134" t="n">
-        <v>0.5424656412832509</v>
+        <v>0.5424512088998875</v>
       </c>
       <c r="E134" t="n">
         <v>1.445579117520115</v>
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.8796889193687918</v>
+        <v>0.8796841850573633</v>
       </c>
       <c r="C136" t="n">
-        <v>0.6375113549500264</v>
+        <v>0.6374734804585971</v>
       </c>
       <c r="D136" t="n">
-        <v>0.5786944762952525</v>
+        <v>0.5809786373213544</v>
       </c>
       <c r="E136" t="n">
         <v>3.015639627636272</v>
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.8597505203799797</v>
+        <v>0.8596265664758047</v>
       </c>
       <c r="C137" t="n">
-        <v>0.4780041630397543</v>
+        <v>0.4770125318063582</v>
       </c>
       <c r="D137" t="n">
-        <v>0.5274553049208245</v>
+        <v>0.5277015863665965</v>
       </c>
       <c r="E137" t="n">
         <v>1.65236624483961</v>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.8518428203251325</v>
+        <v>0.8518044358402032</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4147425626004684</v>
+        <v>0.414435486721031</v>
       </c>
       <c r="D138" t="n">
-        <v>0.5061101109425744</v>
+        <v>0.50633684212566</v>
       </c>
       <c r="E138" t="n">
         <v>1125.929554109362</v>
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.869475000000038</v>
+        <v>0.8698400000000358</v>
       </c>
       <c r="C139" t="n">
-        <v>0.5558000000000088</v>
+        <v>0.5587200000000107</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4600983997295114</v>
+        <v>0.468124994737829</v>
       </c>
       <c r="E139" t="n">
         <v>0.6587684344577635</v>
@@ -3503,13 +3503,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.8655849644647747</v>
+        <v>0.864716502114333</v>
       </c>
       <c r="C140" t="n">
-        <v>0.5246797157178942</v>
+        <v>0.5177320169143221</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4519620818269737</v>
+        <v>0.4546485697454333</v>
       </c>
       <c r="E140" t="n">
         <v>28.12794365228631</v>
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.8616100000000851</v>
+        <v>0.8605450000000932</v>
       </c>
       <c r="C141" t="n">
-        <v>0.4928800000000149</v>
+        <v>0.4843600000000169</v>
       </c>
       <c r="D141" t="n">
-        <v>0.5882872285768947</v>
+        <v>0.5894555853728131</v>
       </c>
       <c r="E141" t="n">
         <v>0.8057320884537136</v>
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4404438018314338</v>
+        <v>0.4402842803710613</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2650206719768123</v>
+        <v>0.2637445002938273</v>
       </c>
       <c r="D142" t="n">
-        <v>0.260398120759633</v>
+        <v>0.2628517921319387</v>
       </c>
       <c r="E142" t="n">
         <v>13.01222477795345</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.8636080249190171</v>
+        <v>0.8628410380649389</v>
       </c>
       <c r="C143" t="n">
-        <v>0.508864199351387</v>
+        <v>0.5027283045187169</v>
       </c>
       <c r="D143" t="n">
-        <v>0.5450078989433496</v>
+        <v>0.5434491030936516</v>
       </c>
       <c r="E143" t="n">
         <v>5.779572148856199</v>
@@ -3591,13 +3591,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.8583400000001077</v>
+        <v>0.8587700000001052</v>
       </c>
       <c r="C144" t="n">
-        <v>0.4667200000000251</v>
+        <v>0.4701600000000222</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4549741353655935</v>
+        <v>0.4576105788711108</v>
       </c>
       <c r="E144" t="n">
         <v>0.01749539952161474</v>
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.8519384338979329</v>
+        <v>0.8519355251756529</v>
       </c>
       <c r="C145" t="n">
-        <v>0.415507471182434</v>
+        <v>0.4154842014041917</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2884273814205724</v>
+        <v>0.2883620225175584</v>
       </c>
       <c r="E145" t="n">
         <v>198.3824296906476</v>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.8702380469372694</v>
+        <v>0.8692998598848483</v>
       </c>
       <c r="C146" t="n">
-        <v>0.5619043754979304</v>
+        <v>0.5543988790785075</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4415348281540162</v>
+        <v>0.4309596762911412</v>
       </c>
       <c r="E146" t="n">
         <v>27.57354284865587</v>
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.8626931095386032</v>
+        <v>0.8621231503205649</v>
       </c>
       <c r="C147" t="n">
-        <v>0.5015448763082001</v>
+        <v>0.496985202563889</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4995821846320924</v>
+        <v>0.4853541171376899</v>
       </c>
       <c r="E147" t="n">
         <v>48.13775538690534</v>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4697878736673969</v>
+        <v>0.4699177772323716</v>
       </c>
       <c r="C148" t="n">
-        <v>0.307188774926179</v>
+        <v>0.3082280034459867</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2421559876971931</v>
+        <v>0.2441821746983268</v>
       </c>
       <c r="E148" t="n">
         <v>10.57800289890836</v>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.8999714277738817</v>
+        <v>0.8999713183746481</v>
       </c>
       <c r="C151" t="n">
-        <v>0.7997714221924928</v>
+        <v>0.7997705469986229</v>
       </c>
       <c r="D151" t="n">
-        <v>0.5397205561277201</v>
+        <v>0.5362150836222147</v>
       </c>
       <c r="E151" t="n">
         <v>393.1793447942276</v>
@@ -3767,13 +3767,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.8559715978175874</v>
+        <v>0.8560878379777596</v>
       </c>
       <c r="C152" t="n">
-        <v>0.4477727825401884</v>
+        <v>0.4487027038215621</v>
       </c>
       <c r="D152" t="n">
-        <v>0.5448267475701216</v>
+        <v>0.5433029512760005</v>
       </c>
       <c r="E152" t="n">
         <v>1.395526392978129</v>
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.8595380397610392</v>
+        <v>0.8586787601802415</v>
       </c>
       <c r="C153" t="n">
-        <v>0.4763043180879186</v>
+        <v>0.4694300814415305</v>
       </c>
       <c r="D153" t="n">
-        <v>0.5726993326274153</v>
+        <v>0.574882824114798</v>
       </c>
       <c r="E153" t="n">
         <v>90.57568579262467</v>
@@ -3811,13 +3811,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.8568913907794193</v>
+        <v>0.8573079119534751</v>
       </c>
       <c r="C154" t="n">
-        <v>0.4551311262344948</v>
+        <v>0.4584632956269662</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4375593853250935</v>
+        <v>0.4452372115727141</v>
       </c>
       <c r="E154" t="n">
         <v>28.57913115437075</v>
@@ -3833,13 +3833,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.1921439274183797</v>
+        <v>0.1918043291683911</v>
       </c>
       <c r="C155" t="n">
-        <v>0.109641872861036</v>
+        <v>0.1069250868611154</v>
       </c>
       <c r="D155" t="n">
-        <v>0.07311390071760243</v>
+        <v>0.06824710839589422</v>
       </c>
       <c r="E155" t="n">
         <v>19.67838081622431</v>
@@ -3855,13 +3855,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.8663010138949917</v>
+        <v>0.8662033694195428</v>
       </c>
       <c r="C156" t="n">
-        <v>0.5304081111595138</v>
+        <v>0.5296269553558967</v>
       </c>
       <c r="D156" t="n">
-        <v>0.5269133261763156</v>
+        <v>0.5318415022402327</v>
       </c>
       <c r="E156" t="n">
         <v>615.9535136188678</v>
@@ -3921,13 +3921,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.4326963927459851</v>
+        <v>0.4320719427725285</v>
       </c>
       <c r="C159" t="n">
-        <v>0.2734778704073813</v>
+        <v>0.2684822706196949</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2897239190789821</v>
+        <v>0.2888363297528029</v>
       </c>
       <c r="E159" t="n">
         <v>225.2377199264863</v>
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.8622327622593755</v>
+        <v>0.8616621344604527</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4978620980743496</v>
+        <v>0.4932970756829475</v>
       </c>
       <c r="D160" t="n">
-        <v>0.5302389868709699</v>
+        <v>0.5296312011954606</v>
       </c>
       <c r="E160" t="n">
         <v>4.726175509562117</v>
@@ -3965,13 +3965,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.8525474057571807</v>
+        <v>0.8524833325726066</v>
       </c>
       <c r="C161" t="n">
-        <v>0.4203792460566976</v>
+        <v>0.4198666605800944</v>
       </c>
       <c r="D161" t="n">
-        <v>0.6040447882441479</v>
+        <v>0.6058655753812932</v>
       </c>
       <c r="E161" t="n">
         <v>0.5021039429104853</v>
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.8870325711309331</v>
+        <v>0.88699757122534</v>
       </c>
       <c r="C162" t="n">
-        <v>0.6962605690482671</v>
+        <v>0.6959805698035226</v>
       </c>
       <c r="D162" t="n">
-        <v>0.5295848701329864</v>
+        <v>0.5283092118179801</v>
       </c>
       <c r="E162" t="n">
         <v>80.31950645530242</v>
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.8626217253666746</v>
+        <v>0.8626261438490683</v>
       </c>
       <c r="C163" t="n">
-        <v>0.5009738029328367</v>
+        <v>0.5010091507919899</v>
       </c>
       <c r="D163" t="n">
-        <v>0.3899837662865192</v>
+        <v>0.3961529658842727</v>
       </c>
       <c r="E163" t="n">
         <v>26.15782509785859</v>
@@ -4031,13 +4031,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.8261934574081961</v>
+        <v>0.8251098983017398</v>
       </c>
       <c r="C164" t="n">
-        <v>0.4830632217060504</v>
+        <v>0.4743947488543405</v>
       </c>
       <c r="D164" t="n">
-        <v>0.5029588740793856</v>
+        <v>0.4938020852034627</v>
       </c>
       <c r="E164" t="n">
         <v>922.013396662938</v>
@@ -4075,13 +4075,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.8566264290802796</v>
+        <v>0.8562452519559688</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4530114326415707</v>
+        <v>0.4499620156470587</v>
       </c>
       <c r="D166" t="n">
-        <v>0.502739368500329</v>
+        <v>0.5035456095103356</v>
       </c>
       <c r="E166" t="n">
         <v>52.30987267565389</v>
@@ -4097,13 +4097,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.861330115854989</v>
+        <v>0.8602106407485928</v>
       </c>
       <c r="C167" t="n">
-        <v>0.4906409268392394</v>
+        <v>0.4816851259880495</v>
       </c>
       <c r="D167" t="n">
-        <v>0.590586912436539</v>
+        <v>0.5944469856742033</v>
       </c>
       <c r="E167" t="n">
         <v>7.108823199983012</v>
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.1155282438278794</v>
+        <v>0.1156597794554575</v>
       </c>
       <c r="C168" t="n">
-        <v>0.07635312989427336</v>
+        <v>0.07740541491490274</v>
       </c>
       <c r="D168" t="n">
-        <v>0.06933947478753533</v>
+        <v>0.07052179766478678</v>
       </c>
       <c r="E168" t="n">
         <v>7.197379656930985</v>
@@ -4163,13 +4163,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.8598306999923018</v>
+        <v>0.86023983766709</v>
       </c>
       <c r="C170" t="n">
-        <v>0.4786455999376625</v>
+        <v>0.4819187013359881</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4388300538619271</v>
+        <v>0.4450362671853688</v>
       </c>
       <c r="E170" t="n">
         <v>11.83241979681551</v>
@@ -4185,13 +4185,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.8658444389115848</v>
+        <v>0.8655301484607412</v>
       </c>
       <c r="C171" t="n">
-        <v>0.5267555112925385</v>
+        <v>0.5242411876857951</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4836895129791491</v>
+        <v>0.4860671184904489</v>
       </c>
       <c r="E171" t="n">
         <v>234.922418167551</v>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.4077274204032058</v>
+        <v>0.40741503916481</v>
       </c>
       <c r="C172" t="n">
-        <v>0.2218521052629165</v>
+        <v>0.2193530553557373</v>
       </c>
       <c r="D172" t="n">
-        <v>0.2151292457866134</v>
+        <v>0.2161511142333204</v>
       </c>
       <c r="E172" t="n">
         <v>449.7799530041226</v>
@@ -4251,13 +4251,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.8986962546996502</v>
+        <v>0.8986780310378943</v>
       </c>
       <c r="C174" t="n">
-        <v>0.7895700375983898</v>
+        <v>0.7894242483043424</v>
       </c>
       <c r="D174" t="n">
-        <v>0.5898435061265535</v>
+        <v>0.5926745338191702</v>
       </c>
       <c r="E174" t="n">
         <v>656.5359530123661</v>
@@ -4273,13 +4273,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.8651204305127368</v>
+        <v>0.8647198177357315</v>
       </c>
       <c r="C175" t="n">
-        <v>0.5209634441016523</v>
+        <v>0.5177585418855962</v>
       </c>
       <c r="D175" t="n">
-        <v>0.580227523936742</v>
+        <v>0.5815644883105815</v>
       </c>
       <c r="E175" t="n">
         <v>192.7468776808428</v>
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.8539174447755451</v>
+        <v>0.8538294620117192</v>
       </c>
       <c r="C176" t="n">
-        <v>0.4313395582038136</v>
+        <v>0.4306356960931867</v>
       </c>
       <c r="D176" t="n">
-        <v>0.6081070587044325</v>
+        <v>0.6086239178975978</v>
       </c>
       <c r="E176" t="n">
         <v>15.3886884429322</v>
@@ -4317,13 +4317,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.8710228000141919</v>
+        <v>0.870903352095308</v>
       </c>
       <c r="C177" t="n">
-        <v>0.568182400113548</v>
+        <v>0.5672268167624767</v>
       </c>
       <c r="D177" t="n">
-        <v>0.5443319453759716</v>
+        <v>0.5464730513393297</v>
       </c>
       <c r="E177" t="n">
         <v>43.52289804519446</v>
@@ -4383,13 +4383,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.8830587697228299</v>
+        <v>0.8828632640699755</v>
       </c>
       <c r="C180" t="n">
-        <v>0.6644701577826314</v>
+        <v>0.6629061125597879</v>
       </c>
       <c r="D180" t="n">
-        <v>0.533307538157607</v>
+        <v>0.5349047766664378</v>
       </c>
       <c r="E180" t="n">
         <v>126.2927300093014</v>
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.8657576216266479</v>
+        <v>0.8651371204018241</v>
       </c>
       <c r="C181" t="n">
-        <v>0.5260609730129721</v>
+        <v>0.5210969632143666</v>
       </c>
       <c r="D181" t="n">
-        <v>0.5459099215660161</v>
+        <v>0.5485142778361909</v>
       </c>
       <c r="E181" t="n">
         <v>470.548678149941</v>
@@ -4427,13 +4427,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.8697329111345661</v>
+        <v>0.8692456686015848</v>
       </c>
       <c r="C182" t="n">
-        <v>0.5578632890765169</v>
+        <v>0.5539653488126662</v>
       </c>
       <c r="D182" t="n">
-        <v>0.5209746059887163</v>
+        <v>0.512829483844399</v>
       </c>
       <c r="E182" t="n">
         <v>1.365522232982848</v>
@@ -4471,13 +4471,13 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.8587835530611664</v>
+        <v>0.8598604245145923</v>
       </c>
       <c r="C184" t="n">
-        <v>0.4702684244885112</v>
+        <v>0.4788833961159586</v>
       </c>
       <c r="D184" t="n">
-        <v>0.5209854562505689</v>
+        <v>0.5246322470962127</v>
       </c>
       <c r="E184" t="n">
         <v>0.1364464571896991</v>
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.869039038378468</v>
+        <v>0.868628287005233</v>
       </c>
       <c r="C185" t="n">
-        <v>0.5523123070275326</v>
+        <v>0.5490262960416309</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4917431603882344</v>
+        <v>0.490974558536469</v>
       </c>
       <c r="E185" t="n">
         <v>0.4697265412884362</v>
@@ -4559,13 +4559,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.8635100000000728</v>
+        <v>0.8635500000000735</v>
       </c>
       <c r="C188" t="n">
-        <v>0.508080000000009</v>
+        <v>0.508400000000013</v>
       </c>
       <c r="D188" t="n">
-        <v>0.5798153172972251</v>
+        <v>0.5811836348863431</v>
       </c>
       <c r="E188" t="n">
         <v>0.01723549625315309</v>
@@ -4581,13 +4581,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.8602676033969348</v>
+        <v>0.8600345674791408</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4821408271754692</v>
+        <v>0.4802765398330958</v>
       </c>
       <c r="D189" t="n">
-        <v>0.5885626520321774</v>
+        <v>0.5905948935277384</v>
       </c>
       <c r="E189" t="n">
         <v>0.08395035339881537</v>
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.8747544305770263</v>
+        <v>0.8743436087569195</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5980354446161874</v>
+        <v>0.5947488700553378</v>
       </c>
       <c r="D192" t="n">
-        <v>0.5665149801407184</v>
+        <v>0.5707107091917493</v>
       </c>
       <c r="E192" t="n">
         <v>398.6350313019615</v>
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.8644922926811506</v>
+        <v>0.8639987711657892</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5159383414486767</v>
+        <v>0.5119901693257463</v>
       </c>
       <c r="D193" t="n">
-        <v>0.5026985875313861</v>
+        <v>0.49259368217171</v>
       </c>
       <c r="E193" t="n">
         <v>13.82781075827447</v>
@@ -4691,13 +4691,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.8644788929477721</v>
+        <v>0.8635557903803615</v>
       </c>
       <c r="C194" t="n">
-        <v>0.5158311435816425</v>
+        <v>0.5084463230423235</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5887016448945697</v>
+        <v>0.5905139475647719</v>
       </c>
       <c r="E194" t="n">
         <v>31.09342868839511</v>
@@ -4713,13 +4713,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.863370000000074</v>
+        <v>0.8639050000000706</v>
       </c>
       <c r="C195" t="n">
-        <v>0.5069600000000127</v>
+        <v>0.5112400000000104</v>
       </c>
       <c r="D195" t="n">
-        <v>0.5676959659413086</v>
+        <v>0.5684841572132293</v>
       </c>
       <c r="E195" t="n">
         <v>0.3914328627343548</v>
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.06737222471572139</v>
+        <v>0.0673869130342286</v>
       </c>
       <c r="C196" t="n">
-        <v>0.04421338484597091</v>
+        <v>0.04433089139402987</v>
       </c>
       <c r="D196" t="n">
-        <v>0.03933993750461796</v>
+        <v>0.03902520839511558</v>
       </c>
       <c r="E196" t="n">
         <v>7.748688533534619</v>
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.8649350000000701</v>
+        <v>0.8661150000000584</v>
       </c>
       <c r="C198" t="n">
-        <v>0.5194800000000084</v>
+        <v>0.5289200000000084</v>
       </c>
       <c r="D198" t="n">
-        <v>0.5557694289673163</v>
+        <v>0.5629497979909943</v>
       </c>
       <c r="E198" t="n">
         <v>0.06946355553166232</v>
@@ -4801,13 +4801,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.8971410266083678</v>
+        <v>0.897098822599915</v>
       </c>
       <c r="C199" t="n">
-        <v>0.7771282128674951</v>
+        <v>0.7767905807998721</v>
       </c>
       <c r="D199" t="n">
-        <v>0.5934552247872007</v>
+        <v>0.5956584185042414</v>
       </c>
       <c r="E199" t="n">
         <v>88.91853159354389</v>
@@ -4823,13 +4823,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.889311912905105</v>
+        <v>0.8892536938433695</v>
       </c>
       <c r="C200" t="n">
-        <v>0.7144953032415078</v>
+        <v>0.71402955074762</v>
       </c>
       <c r="D200" t="n">
-        <v>0.5911612188924651</v>
+        <v>0.5921107974597937</v>
       </c>
       <c r="E200" t="n">
         <v>26.12750684365162</v>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.8602538949176612</v>
+        <v>0.8598697444039517</v>
       </c>
       <c r="C203" t="n">
-        <v>0.4820311593408573</v>
+        <v>0.4789579552311738</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4819211753462626</v>
+        <v>0.482029143402781</v>
       </c>
       <c r="E203" t="n">
         <v>335.0771279167679</v>
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.8925757497674792</v>
+        <v>0.8925776395364882</v>
       </c>
       <c r="C204" t="n">
-        <v>0.7406059981404287</v>
+        <v>0.7406211162925052</v>
       </c>
       <c r="D204" t="n">
-        <v>0.6206854555664755</v>
+        <v>0.6207186563421847</v>
       </c>
       <c r="E204" t="n">
         <v>759.2235514798114</v>
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.1971470575148127</v>
+        <v>0.1969604595391736</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1118672035557078</v>
+        <v>0.1103744197505841</v>
       </c>
       <c r="D205" t="n">
-        <v>0.08360834828888654</v>
+        <v>0.08139477010194057</v>
       </c>
       <c r="E205" t="n">
         <v>3.459918028773189</v>
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.8659047261657694</v>
+        <v>0.8657392606992338</v>
       </c>
       <c r="C206" t="n">
-        <v>0.6759928976146384</v>
+        <v>0.6746691738823524</v>
       </c>
       <c r="D206" t="n">
-        <v>0.5732797801675485</v>
+        <v>0.5748419690091006</v>
       </c>
       <c r="E206" t="n">
         <v>838.8057612466587</v>
@@ -4977,13 +4977,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.8609118414226294</v>
+        <v>0.8607099073715708</v>
       </c>
       <c r="C207" t="n">
-        <v>0.4872947313803214</v>
+        <v>0.4856792589718463</v>
       </c>
       <c r="D207" t="n">
-        <v>0.5018131757942232</v>
+        <v>0.5057821054880405</v>
       </c>
       <c r="E207" t="n">
         <v>8.179133640041659</v>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.8633795337383514</v>
+        <v>0.8631602269938425</v>
       </c>
       <c r="C208" t="n">
-        <v>0.5070362699062108</v>
+        <v>0.5052818159501626</v>
       </c>
       <c r="D208" t="n">
-        <v>0.464006283157098</v>
+        <v>0.4645936954026311</v>
       </c>
       <c r="E208" t="n">
         <v>24.47688807939581</v>
@@ -5065,13 +5065,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.5372784644343016</v>
+        <v>0.5372079178359548</v>
       </c>
       <c r="C211" t="n">
-        <v>0.3959495311682107</v>
+        <v>0.3953851583814353</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3447372009149962</v>
+        <v>0.3475932577517186</v>
       </c>
       <c r="E211" t="n">
         <v>2.33256406289593</v>
@@ -5093,7 +5093,7 @@
         <v>0.8000000000001271</v>
       </c>
       <c r="D212" t="n">
-        <v>0.5520103414078118</v>
+        <v>0.5489972917873578</v>
       </c>
       <c r="E212" t="n">
         <v>266.9079209822854</v>
@@ -5109,13 +5109,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.8706004677237379</v>
+        <v>0.8706492038632768</v>
       </c>
       <c r="C213" t="n">
-        <v>0.5648037417898346</v>
+        <v>0.5651936309061475</v>
       </c>
       <c r="D213" t="n">
-        <v>0.5197981868454874</v>
+        <v>0.5176889073699089</v>
       </c>
       <c r="E213" t="n">
         <v>192.7317837825977</v>
@@ -5131,13 +5131,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.8667192618292343</v>
+        <v>0.8652432317236726</v>
       </c>
       <c r="C214" t="n">
-        <v>0.5337540946336408</v>
+        <v>0.5219458537890814</v>
       </c>
       <c r="D214" t="n">
-        <v>0.5477698766454262</v>
+        <v>0.5477308054626924</v>
       </c>
       <c r="E214" t="n">
         <v>289.123922668091</v>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8598878373049408</v>
+        <v>0.8590374473995934</v>
       </c>
       <c r="C216" t="n">
-        <v>0.4791026984391712</v>
+        <v>0.4722995791963577</v>
       </c>
       <c r="D216" t="n">
-        <v>0.6077892901911462</v>
+        <v>0.6094675340212822</v>
       </c>
       <c r="E216" t="n">
         <v>316.6864743982738</v>
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.7541971593074352</v>
+        <v>0.7531084622265017</v>
       </c>
       <c r="C217" t="n">
-        <v>0.4912771150262612</v>
+        <v>0.4825675383787335</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4813051815096162</v>
+        <v>0.479576186459783</v>
       </c>
       <c r="E217" t="n">
         <v>36.8368047188121</v>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.8625471322587024</v>
+        <v>0.8616431655269456</v>
       </c>
       <c r="C218" t="n">
-        <v>0.5003770580691781</v>
+        <v>0.4931453242151017</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5214512636626323</v>
+        <v>0.5240107265931578</v>
       </c>
       <c r="E218" t="n">
         <v>26.09583648869743</v>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8550223157666913</v>
+        <v>0.85502311742159</v>
       </c>
       <c r="C219" t="n">
-        <v>0.4401785261326714</v>
+        <v>0.4401849393718606</v>
       </c>
       <c r="D219" t="n">
-        <v>0.382253797273563</v>
+        <v>0.3822595402781342</v>
       </c>
       <c r="E219" t="n">
         <v>144.8190819860523</v>
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.3565064658103536</v>
+        <v>0.356294194837025</v>
       </c>
       <c r="C221" t="n">
-        <v>0.1948935101533327</v>
+        <v>0.1931953423666962</v>
       </c>
       <c r="D221" t="n">
-        <v>0.1999875487540217</v>
+        <v>0.198924515874368</v>
       </c>
       <c r="E221" t="n">
         <v>6.952830971413511</v>
@@ -5329,13 +5329,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.864208134920696</v>
+        <v>0.863981388888952</v>
       </c>
       <c r="C223" t="n">
-        <v>0.5136650793650929</v>
+        <v>0.5118511111111237</v>
       </c>
       <c r="D223" t="n">
-        <v>0.3570544848440355</v>
+        <v>0.3531572405601854</v>
       </c>
       <c r="E223" t="n">
         <v>0.2845588902888057</v>
@@ -5351,13 +5351,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.8605474420405769</v>
+        <v>0.8599218939188189</v>
       </c>
       <c r="C224" t="n">
-        <v>0.4843795363240663</v>
+        <v>0.4793751513499531</v>
       </c>
       <c r="D224" t="n">
-        <v>0.5779882275914925</v>
+        <v>0.582500297678324</v>
       </c>
       <c r="E224" t="n">
         <v>2.641633486586371</v>
@@ -5395,13 +5395,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.862016175057419</v>
+        <v>0.8614754660484265</v>
       </c>
       <c r="C226" t="n">
-        <v>0.4961294004589268</v>
+        <v>0.4918037283869749</v>
       </c>
       <c r="D226" t="n">
-        <v>0.4696722388386933</v>
+        <v>0.469636718064935</v>
       </c>
       <c r="E226" t="n">
         <v>796.1186147987993</v>
@@ -5417,13 +5417,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.8833421686944493</v>
+        <v>0.8831274781721414</v>
       </c>
       <c r="C227" t="n">
-        <v>0.6667373495556722</v>
+        <v>0.6650198253771796</v>
       </c>
       <c r="D227" t="n">
-        <v>0.5683473352439465</v>
+        <v>0.5694020224447656</v>
       </c>
       <c r="E227" t="n">
         <v>25.3125125111521</v>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.8669356489454161</v>
+        <v>0.8662932047530281</v>
       </c>
       <c r="C230" t="n">
-        <v>0.5354851915633115</v>
+        <v>0.5303456380241849</v>
       </c>
       <c r="D230" t="n">
-        <v>0.5239361528164219</v>
+        <v>0.5211474417728857</v>
       </c>
       <c r="E230" t="n">
         <v>12.76466311413991</v>
@@ -5505,13 +5505,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.8649286966321612</v>
+        <v>0.8645678556628594</v>
       </c>
       <c r="C231" t="n">
-        <v>0.5194295730569806</v>
+        <v>0.5165428453025582</v>
       </c>
       <c r="D231" t="n">
-        <v>0.5031621015788184</v>
+        <v>0.5075270425446877</v>
       </c>
       <c r="E231" t="n">
         <v>479.2524585891806</v>
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.8641718033432964</v>
+        <v>0.8641489018527339</v>
       </c>
       <c r="C232" t="n">
-        <v>0.5133744267463068</v>
+        <v>0.5131912148217997</v>
       </c>
       <c r="D232" t="n">
-        <v>0.500236083774013</v>
+        <v>0.5045453893086785</v>
       </c>
       <c r="E232" t="n">
         <v>146.8218738567094</v>
@@ -5549,13 +5549,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.8749800106742092</v>
+        <v>0.8745237486082827</v>
       </c>
       <c r="C233" t="n">
-        <v>0.5998400853937041</v>
+        <v>0.5961899888662816</v>
       </c>
       <c r="D233" t="n">
-        <v>0.5589330187255896</v>
+        <v>0.5600829744863929</v>
       </c>
       <c r="E233" t="n">
         <v>1461.644610622728</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8715584557930395</v>
+        <v>0.8715375358293214</v>
       </c>
       <c r="C234" t="n">
-        <v>0.5724676463442622</v>
+        <v>0.572300286634518</v>
       </c>
       <c r="D234" t="n">
-        <v>0.5715035769307829</v>
+        <v>0.5714583963969339</v>
       </c>
       <c r="E234" t="n">
         <v>9591.141011544092</v>
@@ -5593,13 +5593,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.8587141976749917</v>
+        <v>0.8581545852941386</v>
       </c>
       <c r="C235" t="n">
-        <v>0.4697135813992217</v>
+        <v>0.4652366823523784</v>
       </c>
       <c r="D235" t="n">
-        <v>0.5871057191228387</v>
+        <v>0.5892410993996545</v>
       </c>
       <c r="E235" t="n">
         <v>19.59454425503996</v>
@@ -5615,13 +5615,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.8746652632186646</v>
+        <v>0.8743063684978019</v>
       </c>
       <c r="C236" t="n">
-        <v>0.5973221057492883</v>
+        <v>0.5944509479823804</v>
       </c>
       <c r="D236" t="n">
-        <v>0.559754579094048</v>
+        <v>0.5673630724347225</v>
       </c>
       <c r="E236" t="n">
         <v>117.9602492240784</v>
@@ -5681,13 +5681,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.8591383334323528</v>
+        <v>0.8584759974343542</v>
       </c>
       <c r="C239" t="n">
-        <v>0.4731066674582522</v>
+        <v>0.467807979474223</v>
       </c>
       <c r="D239" t="n">
-        <v>0.5494245672939794</v>
+        <v>0.5542792808691082</v>
       </c>
       <c r="E239" t="n">
         <v>73.7352660142827</v>
@@ -5703,13 +5703,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.8627649197610695</v>
+        <v>0.8627725268273261</v>
       </c>
       <c r="C240" t="n">
-        <v>0.502119358088987</v>
+        <v>0.5021802146190401</v>
       </c>
       <c r="D240" t="n">
-        <v>0.498671820505049</v>
+        <v>0.4986135511498962</v>
       </c>
       <c r="E240" t="n">
         <v>232.9753217574645</v>
@@ -5725,13 +5725,13 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.8706585291910075</v>
+        <v>0.8706260987477569</v>
       </c>
       <c r="C241" t="n">
-        <v>0.5652682335274946</v>
+        <v>0.5650087899814864</v>
       </c>
       <c r="D241" t="n">
-        <v>0.5393635796972416</v>
+        <v>0.5392927439925327</v>
       </c>
       <c r="E241" t="n">
         <v>0.2584788908543458</v>
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.8644582889018103</v>
+        <v>0.8637737680695944</v>
       </c>
       <c r="C245" t="n">
-        <v>0.5156663112141169</v>
+        <v>0.5101901445563832</v>
       </c>
       <c r="D245" t="n">
-        <v>0.5242355349739368</v>
+        <v>0.5245592607294953</v>
       </c>
       <c r="E245" t="n">
         <v>52.71693664316579</v>
@@ -5835,13 +5835,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.8698478983623634</v>
+        <v>0.8688012390204095</v>
       </c>
       <c r="C246" t="n">
-        <v>0.5587831868987111</v>
+        <v>0.5504099121630449</v>
       </c>
       <c r="D246" t="n">
-        <v>0.4867124559777072</v>
+        <v>0.4822254792486239</v>
       </c>
       <c r="E246" t="n">
         <v>111.1899758838198</v>
